--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2436-13-CM26</t>
+          <t>5178-89-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,32 +1510,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>11744.05</v>
+        <v>811.9299999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5178-89-CM26</t>
+          <t>2436-13-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1571,32 +1571,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>811.9299999999999</v>
+        <v>11744.05</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>116108.0025</v>
+        <v>116108</v>
       </c>
     </row>
     <row r="21">
@@ -1982,7 +1982,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3157-2-CM26</t>
+          <t>3945-4-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2007,27 +2007,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIRECCION DE SANIDAD DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>234.78</v>
+        <v>2166.95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4469-9-CM26</t>
+          <t>5394-12-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2063,32 +2063,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4938.12</v>
+        <v>22595.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4469-8-CM26</t>
+          <t>2412-14-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8613.219999999999</v>
+        <v>221.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4469-7-CM26</t>
+          <t>564162-53-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2185,32 +2185,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>10317.3</v>
+        <v>9524.059999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>564162-53-CM26</t>
+          <t>3659-19-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>9524.059999999999</v>
+        <v>18179.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3945-4-CM26</t>
+          <t>4469-7-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2307,32 +2307,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2166.95</v>
+        <v>10317.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2412-14-CM26</t>
+          <t>4469-8-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2368,32 +2368,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>221.79</v>
+        <v>8613.219999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5394-12-CM26</t>
+          <t>4469-9-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2429,32 +2429,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>22595.53</v>
+        <v>4938.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3659-19-CM26</t>
+          <t>3157-2-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2490,32 +2490,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>DIRECCION DE SANIDAD DE LA ARMADA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>18179.33</v>
+        <v>234.78</v>
       </c>
     </row>
     <row r="35">
@@ -2592,7 +2592,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1075952-5-CM26</t>
+          <t>1002584-18-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.000.580-0</t>
+          <t>65.154.016-k</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Superintendencia de Educación Superior</t>
+          <t>DIRECCION DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>8130.01</v>
+        <v>5320.01</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1002584-18-CM26</t>
+          <t>1075952-5-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.154.016-k</t>
+          <t>62.000.580-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION PUBLICA</t>
+          <t>Superintendencia de Educación Superior</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5320.01</v>
+        <v>8130.01</v>
       </c>
     </row>
     <row r="38">
@@ -2775,7 +2775,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1109692-9-CM26</t>
+          <t>1002584-17-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2800,27 +2800,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>65.154.016-k</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>DIRECCION DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>648.55</v>
+        <v>4426.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3723-4-CM26</t>
+          <t>1109692-9-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2856,32 +2856,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1009.12</v>
+        <v>648.55</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3723-3-CM26</t>
+          <t>3723-4-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>791</v>
+        <v>1009.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1002584-17-CM26</t>
+          <t>3723-3-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2978,32 +2978,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>65.154.016-k</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION PUBLICA</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4426.8</v>
+        <v>791</v>
       </c>
     </row>
     <row r="43">
@@ -3385,7 +3385,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2432-19-CM26</t>
+          <t>1658-60-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3410,27 +3410,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>31892</v>
+        <v>3099.95</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2687-2-CM26</t>
+          <t>2432-19-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3466,32 +3466,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>8306.200000000001</v>
+        <v>31892</v>
       </c>
     </row>
     <row r="51">
@@ -3568,7 +3568,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1658-60-CM26</t>
+          <t>1305504-7-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3593,27 +3593,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3099.95</v>
+        <v>1066.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1305504-7-CM26</t>
+          <t>218-15-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3654,27 +3654,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>69.254.600-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>I MUNICIPALIDAD SAN JOAQUIN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1066.8</v>
+        <v>18564</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>218-15-CM26</t>
+          <t>218-14-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>18564</v>
+        <v>11823.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>218-14-CM26</t>
+          <t>2565-30-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3776,27 +3776,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.254.600-8</t>
+          <t>69.090.700-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD SAN JOAQUIN</t>
+          <t>I MUNICIPALIDAD DE CHEPICA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>11823.7</v>
+        <v>3217.76</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2565-30-CM26</t>
+          <t>4469-19-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3832,32 +3832,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.090.700-3</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHEPICA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3217.76</v>
+        <v>3122.87</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4469-19-CM26</t>
+          <t>4469-24-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3122.87</v>
+        <v>3427.2</v>
       </c>
     </row>
     <row r="58">
@@ -4056,7 +4056,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4469-24-CM26</t>
+          <t>2412-31-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4076,32 +4076,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3427.2</v>
+        <v>17136</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2412-31-CM26</t>
+          <t>2778-5-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4137,32 +4137,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>17136</v>
+        <v>2866.35</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4451-49-CM26</t>
+          <t>3894-3-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4198,32 +4198,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>14238.09</v>
+        <v>29709.54</v>
       </c>
     </row>
     <row r="63">
@@ -4361,7 +4361,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2778-5-CM26</t>
+          <t>4451-49-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2866.35</v>
+        <v>14238.09</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3894-3-CM26</t>
+          <t>2467-4-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>29709.54</v>
+        <v>17776.22</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2581-3-CM26</t>
+          <t>2307-101-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4508,27 +4508,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.070.200-2</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCHALI</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>23730.15</v>
+        <v>2538.94</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2467-4-CM26</t>
+          <t>1456839-2-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4564,32 +4564,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.981.420-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>17776.22</v>
+        <v>3768.21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2307-101-CM26</t>
+          <t>3836-34-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4625,32 +4625,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.191.400-3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE TOLTEN</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2538.94</v>
+        <v>69969.62</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1456839-2-CM26</t>
+          <t>2581-3-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.981.420-7</t>
+          <t>69.070.200-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
+          <t>I MUNICIPALIDAD DE CONCHALI</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3768.21</v>
+        <v>23730.15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3836-34-CM26</t>
+          <t>2765-4-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4742,37 +4742,37 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>69969.62</v>
+        <v>16283.96</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3561-7-CM26</t>
+          <t>5178-278-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4808,32 +4808,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>PRODUCTOS Y SERVICIOS INFORMATICOS TORRES SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.229.656-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9637.51</v>
+        <v>761.72</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2765-4-CM26</t>
+          <t>568963-18-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.979.610-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>COMISION DEL SISTEMA NACIONAL DE CERTIFICACION DE COMPETENCIAS LABORALES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>16283.96</v>
+        <v>13718.61</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5178-278-CM26</t>
+          <t>1050283-47-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4930,32 +4930,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>761.72</v>
+        <v>14592.91</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1050283-47-CM26</t>
+          <t>1053139-4-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4996,27 +4996,27 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5026,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>14592.91</v>
+        <v>3936.42</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1053139-4-CM26</t>
+          <t>3561-7-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5057,27 +5057,27 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>PRODUCTOS Y SERVICIOS INFORMATICOS TORRES SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.229.656-8</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3936.42</v>
+        <v>9637.51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>568963-18-CM26</t>
+          <t>1134432-36-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5118,27 +5118,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.979.610-1</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>COMISION DEL SISTEMA NACIONAL DE CERTIFICACION DE COMPETENCIAS LABORALES</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>13718.61</v>
+        <v>520.63</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1134432-36-CM26</t>
+          <t>1134432-34-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>520.63</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1134432-34-CM26</t>
+          <t>377-24-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2835</v>
+        <v>15993.52</v>
       </c>
     </row>
     <row r="80">
@@ -5398,7 +5398,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>377-24-CM26</t>
+          <t>1375757-6-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5423,27 +5423,27 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>15993.52</v>
+        <v>23341.37</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1375757-6-CM26</t>
+          <t>2341-25-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5474,22 +5474,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>23341.37</v>
+        <v>38615.98</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2341-25-CM26</t>
+          <t>2318-50-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5540,32 +5540,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>38615.98</v>
+        <v>19390.91</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2318-50-CM26</t>
+          <t>5067-303-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5606,27 +5606,27 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,13 +5636,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>19390.91</v>
+        <v>17402.11</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5067-303-CM26</t>
+          <t>568963-20-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.979.610-1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>COMISION DEL SISTEMA NACIONAL DE CERTIFICACION DE COMPETENCIAS LABORALES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>17402.11</v>
+        <v>776.48</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>568963-20-CM26</t>
+          <t>1314-5-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.979.610-1</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>COMISION DEL SISTEMA NACIONAL DE CERTIFICACION DE COMPETENCIAS LABORALES</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>IMPORTACIONES Y SERVICIOS ADVANCED COMPUTING TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.609.940-2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>776.48</v>
+        <v>8949.280000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1314-5-CM26</t>
+          <t>2418-2-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5784,32 +5784,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>IMPORTACIONES Y SERVICIOS ADVANCED COMPUTING TECHNOLOGIES S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.609.940-2</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8949.280000000001</v>
+        <v>5704.62</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2418-2-CM26</t>
+          <t>3690-17-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5845,32 +5845,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5704.62</v>
+        <v>2479.94</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3690-17-CM26</t>
+          <t>3690-16-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2479.94</v>
+        <v>6500.86</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3690-16-CM26</t>
+          <t>5178-284-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5967,32 +5967,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>6500.86</v>
+        <v>791</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5178-284-CM26</t>
+          <t>2380-100-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6023,37 +6023,37 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>791</v>
+        <v>35329.61</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>923000-3-CM26</t>
+          <t>1232565-35-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6089,32 +6089,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5464.4</v>
+        <v>1239.96</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1177296-27-CM26</t>
+          <t>5178-312-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6150,17 +6150,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>76798.77</v>
+        <v>797.35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1232565-35-CM26</t>
+          <t>923000-3-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6211,32 +6211,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1239.96</v>
+        <v>5464.4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5178-312-CM26</t>
+          <t>2427-38-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6272,32 +6272,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>797.35</v>
+        <v>72578.10000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6374,7 +6374,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2380-100-CM26</t>
+          <t>1216062-109-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6394,32 +6394,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>35329.61</v>
+        <v>3208.36</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1305543-10-CM26</t>
+          <t>3436-41-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>61.101.027-3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6750.52</v>
+        <v>13751.64</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1216062-109-CM26</t>
+          <t>2279-13-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3208.36</v>
+        <v>3587.83</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3436-41-CM26</t>
+          <t>2910-4-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6582,27 +6582,27 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.101.027-3</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>13751.64</v>
+        <v>8957</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2279-13-CM26</t>
+          <t>1305543-10-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3587.83</v>
+        <v>6750.52</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2910-4-CM26</t>
+          <t>3577-11-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6694,37 +6694,37 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.929.100-K</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>Direccion Admin. Salud Municipal Florida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8957</v>
+        <v>3177.16</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2427-38-CM26</t>
+          <t>1182705-20-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6755,37 +6755,37 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>65.199.131-5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>72578.10000000001</v>
+        <v>6028.9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1182705-20-CM26</t>
+          <t>3384-31-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6826,27 +6826,27 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>65.199.131-5</t>
+          <t>81.448.600-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
+          <t>INSTITUTO GEOGRAFICO MILITAR</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6028.9</v>
+        <v>797.29</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3384-31-CM26</t>
+          <t>5178-335-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>81.448.600-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>INSTITUTO GEOGRAFICO MILITAR</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>797.29</v>
+        <v>956.36</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5178-335-CM26</t>
+          <t>584146-25-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6943,32 +6943,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>956.36</v>
+        <v>2435.78</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>584146-25-CM26</t>
+          <t>1501728-2-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7009,27 +7009,27 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Departamento de Salud Municipal</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2435.78</v>
+        <v>14145.32</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1007793-13-CM26</t>
+          <t>4455-15-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7065,32 +7065,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.999.290-3</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1365.07</v>
+        <v>9330.67</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3577-11-CM26</t>
+          <t>3827-45-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7126,17 +7126,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.929.100-K</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Direccion Admin. Salud Municipal Florida</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3177.16</v>
+        <v>5637.95</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1501728-2-CM26</t>
+          <t>3928-27-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7187,17 +7187,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Departamento de Salud Municipal</t>
+          <t>Educación Municipal</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>14145.32</v>
+        <v>6943.65</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3827-45-CM26</t>
+          <t>2580-19-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5637.95</v>
+        <v>2082.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3928-27-CM26</t>
+          <t>1007793-13-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7309,32 +7309,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>61.999.290-3</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6943.65</v>
+        <v>1365.07</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2580-19-CM26</t>
+          <t>2909-32-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7375,27 +7375,27 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2082.5</v>
+        <v>5829.81</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4455-15-CM26</t>
+          <t>4469-65-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7426,37 +7426,37 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>9330.67</v>
+        <v>5469.24</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2909-32-CM26</t>
+          <t>4469-63-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7492,32 +7492,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>5829.81</v>
+        <v>1965.86</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1237328-16-CM26</t>
+          <t>2385-40-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7553,22 +7553,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>7934.44</v>
+        <v>4914.64</v>
       </c>
     </row>
     <row r="118">
@@ -7655,7 +7655,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2675-21-CM26</t>
+          <t>1237328-16-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7675,22 +7675,22 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>11373.81</v>
+        <v>7934.44</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2385-40-CM26</t>
+          <t>5178-366-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7741,27 +7741,27 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4914.64</v>
+        <v>4629.1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2727-54-CM26</t>
+          <t>2580-21-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7797,32 +7797,32 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4583.88</v>
+        <v>12399.68</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4469-65-CM26</t>
+          <t>948354-162-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7858,32 +7858,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5469.24</v>
+        <v>8234.799999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4469-63-CM26</t>
+          <t>799512-29-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7919,17 +7919,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1965.86</v>
+        <v>5011.09</v>
       </c>
     </row>
     <row r="124">
@@ -8021,7 +8021,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5178-363-CM26</t>
+          <t>2961-51-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.400-6</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2314.55</v>
+        <v>6132.88</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>948354-162-CM26</t>
+          <t>2580-20-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8234.799999999999</v>
+        <v>18754.16</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>799512-29-CM26</t>
+          <t>744835-23-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8168,27 +8168,27 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>69.255.100-1</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>5011.09</v>
+        <v>2479.94</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2961-51-CM26</t>
+          <t>5178-363-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8259,13 +8259,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>6132.88</v>
+        <v>2314.55</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2580-21-CM26</t>
+          <t>2324-105-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8290,27 +8290,27 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8320,13 +8320,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>12399.68</v>
+        <v>10667.21</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2580-20-CM26</t>
+          <t>2324-104-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8351,27 +8351,27 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>18754.16</v>
+        <v>2260.41</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>744835-23-CM26</t>
+          <t>1071775-14-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8412,27 +8412,27 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.255.100-1</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2479.94</v>
+        <v>12852</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5178-366-CM26</t>
+          <t>2833-100-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8463,37 +8463,37 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.930.600-7</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>4629.1</v>
+        <v>17445.4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2324-105-CM26</t>
+          <t>2935-17-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8529,32 +8529,32 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>10667.21</v>
+        <v>10234.02</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2324-104-CM26</t>
+          <t>1080936-23-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8595,27 +8595,27 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.506.012-9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>Fondos Extrapresupuestarios Escipol</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2260.41</v>
+        <v>51973.25</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1071775-14-CM26</t>
+          <t>3994-16-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8656,27 +8656,27 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>12852</v>
+        <v>6131.48</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2833-100-CM26</t>
+          <t>3110-18-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8712,17 +8712,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.930.600-7</t>
+          <t>61.102.033-3</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>DIRECCION DE BIENESTAR SOCIAL DE LA ARMADA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>17445.4</v>
+        <v>442.63</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2935-17-CM26</t>
+          <t>3110-17-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8773,32 +8773,32 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>61.102.033-3</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>DIRECCION DE BIENESTAR SOCIAL DE LA ARMADA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8808,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>10234.02</v>
+        <v>4319.63</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1080936-23-CM26</t>
+          <t>2577-3-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.506.012-9</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fondos Extrapresupuestarios Escipol</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ASOPCON LIMITADA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.404.551-3</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>51973.25</v>
+        <v>3570.83</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3994-16-CM26</t>
+          <t>2577-2-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8900,27 +8900,27 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6131.48</v>
+        <v>28183.6</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3110-18-CM26</t>
+          <t>2577-1-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8961,27 +8961,27 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.102.033-3</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DIRECCION DE BIENESTAR SOCIAL DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>442.63</v>
+        <v>11051.41</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3110-17-CM26</t>
+          <t>2328-44-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9022,27 +9022,27 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.102.033-3</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DIRECCION DE BIENESTAR SOCIAL DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4319.63</v>
+        <v>51170.12</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2577-3-CM26</t>
+          <t>5756-69-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ASOPCON LIMITADA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.404.551-3</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3570.83</v>
+        <v>37173.55</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2577-2-CM26</t>
+          <t>1339159-8-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.981.070-8</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>Servicio Local de Educación Pública Santa Rosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>28183.6</v>
+        <v>80250.03</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2577-1-CM26</t>
+          <t>1298354-25-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIRECCION DE EDUCACION</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>11051.41</v>
+        <v>10292.16</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2328-44-CM26</t>
+          <t>1725-41-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>51170.12</v>
+        <v>37197.62</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5756-69-CM26</t>
+          <t>2322-61-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9327,27 +9327,27 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>37173.55</v>
+        <v>1141.44</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1339159-8-CM26</t>
+          <t>2682-45-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.981.070-8</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>80250.03</v>
+        <v>7928.93</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5178-431-CM26</t>
+          <t>539119-317-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9444,17 +9444,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>616.41</v>
+        <v>7382.45</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1298354-25-CM26</t>
+          <t>4359-7-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9505,32 +9505,32 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>10292.16</v>
+        <v>6126.12</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1725-41-CM26</t>
+          <t>2306-11-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9566,32 +9566,32 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>37197.62</v>
+        <v>31225.6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2322-61-CM26</t>
+          <t>599-11-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9632,27 +9632,27 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1141.44</v>
+        <v>1961.12</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2682-45-CM26</t>
+          <t>2703-39-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>7928.93</v>
+        <v>7288.42</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>539119-317-CM26</t>
+          <t>4856-15-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9754,17 +9754,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>7382.45</v>
+        <v>248.02</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4359-7-CM26</t>
+          <t>1725-47-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9805,37 +9805,37 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9845,13 +9845,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>6126.12</v>
+        <v>32106.2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2306-11-CM26</t>
+          <t>3299-26-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9876,27 +9876,27 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9906,13 +9906,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>31225.6</v>
+        <v>6680.51</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>599-11-CM26</t>
+          <t>1485465-4-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9927,37 +9927,37 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9967,372 +9967,6 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1961.12</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2703-39-CM26</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>69.071.800-6</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M157" s="2" t="n">
-        <v>7288.42</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2792-25-CM26</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>No aceptada</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>69.255.400-0</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>COBROTECH SPA</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>76.819.088-7</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M158" s="2" t="n">
-        <v>763.98</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>4856-15-CM26</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>69.160.700-3</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Bío-Bío</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M159" s="2" t="n">
-        <v>248.02</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>1725-47-CM26</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>60.901.002-9</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>COMPUNOW SPA</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>78.218.816-K</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M160" s="2" t="n">
-        <v>32106.2</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>3299-26-CM26</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>69.100.500-3</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>COMPUTACION INTEGRAL S A</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M161" s="2" t="n">
-        <v>6680.51</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>1485465-4-CM26</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>69.253.500-6</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>NET NOW S.A.</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M162" s="2" t="n">
         <v>10142.91</v>
       </c>
     </row>
